--- a/technology_surveys/004_marine_engine_performance_survey--technology_surveys.xlsx
+++ b/technology_surveys/004_marine_engine_performance_survey--technology_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'model_1',_'label':_'model_1'}</t>
+          <t>model_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Model 1', 'label': 'Model 1'}</t>
+          <t>Model 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'model_2',_'label':_'model_2'}</t>
+          <t>model_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Model 2', 'label': 'Model 2'}</t>
+          <t>Model 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'model_3',_'label':_'model_3'}</t>
+          <t>model_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Model 3', 'label': 'Model 3'}</t>
+          <t>Model 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'normal',_'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Normal', 'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'abnormal',_'label':_'abnormal'}</t>
+          <t>abnormal</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Abnormal', 'label': 'Abnormal'}</t>
+          <t>Abnormal</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'critical',_'label':_'critical'}</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Critical', 'label': 'Critical'}</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'diesel',_'label':_'diesel'}</t>
+          <t>diesel</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Diesel', 'label': 'Diesel'}</t>
+          <t>Diesel</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'gasoline',_'label':_'gasoline'}</t>
+          <t>gasoline</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Gasoline', 'label': 'Gasoline'}</t>
+          <t>Gasoline</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'hybrid',_'label':_'hybrid'}</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Hybrid', 'label': 'Hybrid'}</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'low',_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Low', 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'high',_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'High', 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'regular',_'label':_'regular'}</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Regular', 'label': 'Regular'}</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'intermittent',_'label':_'intermittent'}</t>
+          <t>intermittent</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Intermittent', 'label': 'Intermittent'}</t>
+          <t>Intermittent</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'critical',_'label':_'critical'}</t>
+          <t>critical</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Critical', 'label': 'Critical'}</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'synthetic',_'label':_'synthetic'}</t>
+          <t>synthetic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Synthetic', 'label': 'Synthetic'}</t>
+          <t>Synthetic</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'regular',_'label':_'regular'}</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Regular', 'label': 'Regular'}</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'diesel',_'label':_'diesel'}</t>
+          <t>diesel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Diesel', 'label': 'Diesel'}</t>
+          <t>Diesel</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'manual',_'label':_'manual'}</t>
+          <t>manual</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Manual', 'label': 'Manual'}</t>
+          <t>Manual</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'automatic',_'label':_'automatic'}</t>
+          <t>automatic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Automatic', 'label': 'Automatic'}</t>
+          <t>Automatic</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'front_wheel',_'label':_'front_wheel'}</t>
+          <t>front_wheel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Front wheel', 'label': 'Front wheel'}</t>
+          <t>Front wheel</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'rear_wheel',_'label':_'rear_wheel'}</t>
+          <t>rear_wheel</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Rear wheel', 'label': 'Rear wheel'}</t>
+          <t>Rear wheel</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'all_wheel_drive',_'label':_'all_wheel_drive'}</t>
+          <t>all_wheel_drive</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'All wheel drive', 'label': 'All wheel drive'}</t>
+          <t>All wheel drive</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'valid',_'label':_'valid'}</t>
+          <t>valid</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Valid', 'label': 'Valid'}</t>
+          <t>Valid</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'invalid',_'label':_'invalid'}</t>
+          <t>invalid</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Invalid', 'label': 'Invalid'}</t>
+          <t>Invalid</t>
         </is>
       </c>
     </row>
